--- a/results_all_studies/runtime_summary.xlsx
+++ b/results_all_studies/runtime_summary.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,63 +510,125 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Per-category GP</t>
+          <t>Categorical GP</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1080</v>
       </c>
       <c r="C3" t="n">
-        <v>32.46</v>
+        <v>42.33</v>
       </c>
       <c r="D3" t="n">
-        <v>15.94</v>
+        <v>39.79</v>
       </c>
       <c r="E3" t="n">
-        <v>26.77</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>12.49</v>
+        <v>29.4</v>
       </c>
       <c r="G3" t="n">
-        <v>101.6</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>584.34</v>
+        <v>761.86</v>
       </c>
       <c r="I3" t="n">
-        <v>9.74</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Categorical GP</t>
+          <t>BoTorch acqf</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1080</v>
       </c>
       <c r="C4" t="n">
-        <v>42.33</v>
+        <v>84.66</v>
       </c>
       <c r="D4" t="n">
-        <v>39.79</v>
+        <v>75.22</v>
       </c>
       <c r="E4" t="n">
-        <v>9.119999999999999</v>
+        <v>21.17</v>
       </c>
       <c r="F4" t="n">
-        <v>29.4</v>
+        <v>32.15</v>
       </c>
       <c r="G4" t="n">
-        <v>74.01000000000001</v>
+        <v>144.66</v>
       </c>
       <c r="H4" t="n">
-        <v>761.86</v>
+        <v>1523.84</v>
       </c>
       <c r="I4" t="n">
-        <v>12.7</v>
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Per-category GP</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C5" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="D5" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="E5" t="n">
+        <v>26.77</v>
+      </c>
+      <c r="F5" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="G5" t="n">
+        <v>101.6</v>
+      </c>
+      <c r="H5" t="n">
+        <v>584.34</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.74</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>HGPR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1080</v>
+      </c>
+      <c r="C6" t="n">
+        <v>75.70999999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>72.15000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="F6" t="n">
+        <v>53.71</v>
+      </c>
+      <c r="G6" t="n">
+        <v>128.03</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1362.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>22.71</v>
       </c>
     </row>
   </sheetData>
@@ -580,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,33 +681,65 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Per-category GP</t>
+          <t>Categorical GP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.1</v>
+        <v>42.7</v>
       </c>
       <c r="C3" t="n">
-        <v>31.5</v>
+        <v>42.8</v>
       </c>
       <c r="D3" t="n">
-        <v>30.8</v>
+        <v>41.4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Categorical GP</t>
+          <t>BoTorch acqf</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>42.8</v>
+        <v>84.5</v>
       </c>
       <c r="D4" t="n">
-        <v>41.4</v>
+        <v>85.3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Per-category GP</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>35.1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>HGPR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>69.40000000000001</v>
+      </c>
+      <c r="C6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D6" t="n">
+        <v>83.7</v>
       </c>
     </row>
   </sheetData>

--- a/results_all_studies/runtime_summary.xlsx
+++ b/results_all_studies/runtime_summary.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,125 +510,63 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Categorical GP</t>
+          <t>Per-category GP</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>1080</v>
       </c>
       <c r="C3" t="n">
-        <v>42.33</v>
+        <v>32.46</v>
       </c>
       <c r="D3" t="n">
-        <v>39.79</v>
+        <v>15.94</v>
       </c>
       <c r="E3" t="n">
-        <v>9.119999999999999</v>
+        <v>26.77</v>
       </c>
       <c r="F3" t="n">
-        <v>29.4</v>
+        <v>12.49</v>
       </c>
       <c r="G3" t="n">
-        <v>74.01000000000001</v>
+        <v>101.6</v>
       </c>
       <c r="H3" t="n">
-        <v>761.86</v>
+        <v>584.34</v>
       </c>
       <c r="I3" t="n">
-        <v>12.7</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>BoTorch acqf</t>
+          <t>Categorical GP</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>1080</v>
       </c>
       <c r="C4" t="n">
-        <v>84.66</v>
+        <v>42.33</v>
       </c>
       <c r="D4" t="n">
-        <v>75.22</v>
+        <v>39.79</v>
       </c>
       <c r="E4" t="n">
-        <v>21.17</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>32.15</v>
+        <v>29.4</v>
       </c>
       <c r="G4" t="n">
-        <v>144.66</v>
+        <v>74.01000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>1523.84</v>
+        <v>761.86</v>
       </c>
       <c r="I4" t="n">
-        <v>25.4</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Per-category GP</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1080</v>
-      </c>
-      <c r="C5" t="n">
-        <v>32.46</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15.94</v>
-      </c>
-      <c r="E5" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="F5" t="n">
-        <v>12.49</v>
-      </c>
-      <c r="G5" t="n">
-        <v>101.6</v>
-      </c>
-      <c r="H5" t="n">
-        <v>584.34</v>
-      </c>
-      <c r="I5" t="n">
-        <v>9.74</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>HGPR</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1080</v>
-      </c>
-      <c r="C6" t="n">
-        <v>75.70999999999999</v>
-      </c>
-      <c r="D6" t="n">
-        <v>72.15000000000001</v>
-      </c>
-      <c r="E6" t="n">
-        <v>16.28</v>
-      </c>
-      <c r="F6" t="n">
-        <v>53.71</v>
-      </c>
-      <c r="G6" t="n">
-        <v>128.03</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1362.8</v>
-      </c>
-      <c r="I6" t="n">
-        <v>22.71</v>
+        <v>12.7</v>
       </c>
     </row>
   </sheetData>
@@ -642,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -681,65 +619,33 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Categorical GP</t>
+          <t>Per-category GP</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.7</v>
+        <v>35.1</v>
       </c>
       <c r="C3" t="n">
-        <v>42.8</v>
+        <v>31.5</v>
       </c>
       <c r="D3" t="n">
-        <v>41.4</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>BoTorch acqf</t>
+          <t>Categorical GP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>84.09999999999999</v>
+        <v>42.7</v>
       </c>
       <c r="C4" t="n">
-        <v>84.5</v>
+        <v>42.8</v>
       </c>
       <c r="D4" t="n">
-        <v>85.3</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Per-category GP</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>35.1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="D5" t="n">
-        <v>30.8</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>HGPR</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="C6" t="n">
-        <v>74</v>
-      </c>
-      <c r="D6" t="n">
-        <v>83.7</v>
+        <v>41.4</v>
       </c>
     </row>
   </sheetData>
